--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -34757,6 +34757,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1496" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C1496" t="n">
+        <v>1.79499995708466</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>1.7849999666214</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="G1496" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -34780,6 +34780,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1497" t="n">
+        <v>18900</v>
+      </c>
+      <c r="C1497" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="G1497" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -34803,6 +34803,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1498">
+      <c r="A1498" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1498" t="n">
+        <v>18900</v>
+      </c>
+      <c r="C1498" t="n">
+        <v>1.73500001430511</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>1.71000003814697</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>1.66499996185303</v>
+      </c>
+      <c r="G1498" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -34826,6 +34826,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1499" t="n">
+        <v>11700</v>
+      </c>
+      <c r="C1499" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>1.69500005245209</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="G1499" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -34667,22 +34667,22 @@
     </row>
     <row r="1492">
       <c r="A1492" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1492" t="n">
-        <v>28800</v>
+        <v>8100</v>
       </c>
       <c r="C1492" t="n">
-        <v>1.85000002384186</v>
+        <v>1.89999997615814</v>
       </c>
       <c r="D1492" t="n">
-        <v>1.74500000476837</v>
+        <v>1.83500003814697</v>
       </c>
       <c r="E1492" t="n">
-        <v>1.85000002384186</v>
+        <v>1.89999997615814</v>
       </c>
       <c r="F1492" t="n">
-        <v>1.80999994277954</v>
+        <v>1.86500000953674</v>
       </c>
       <c r="G1492" t="s">
         <v>7</v>
@@ -34690,22 +34690,22 @@
     </row>
     <row r="1493">
       <c r="A1493" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1493" t="n">
-        <v>3600</v>
+        <v>28800</v>
       </c>
       <c r="C1493" t="n">
-        <v>1.77999997138977</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="D1493" t="n">
-        <v>1.77999997138977</v>
+        <v>1.74500000476837</v>
       </c>
       <c r="E1493" t="n">
-        <v>1.77999997138977</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="F1493" t="n">
-        <v>1.77999997138977</v>
+        <v>1.80999994277954</v>
       </c>
       <c r="G1493" t="s">
         <v>7</v>
@@ -34713,22 +34713,22 @@
     </row>
     <row r="1494">
       <c r="A1494" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1494" t="n">
-        <v>9900</v>
+        <v>3600</v>
       </c>
       <c r="C1494" t="n">
-        <v>1.82500004768372</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="D1494" t="n">
-        <v>1.77499997615814</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="E1494" t="n">
-        <v>1.80999994277954</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="F1494" t="n">
-        <v>1.82500004768372</v>
+        <v>1.77999997138977</v>
       </c>
       <c r="G1494" t="s">
         <v>7</v>
@@ -34736,22 +34736,22 @@
     </row>
     <row r="1495">
       <c r="A1495" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1495" t="n">
-        <v>35100</v>
+        <v>9900</v>
       </c>
       <c r="C1495" t="n">
-        <v>1.85000002384186</v>
+        <v>1.82500004768372</v>
       </c>
       <c r="D1495" t="n">
-        <v>1.82000005245209</v>
+        <v>1.77499997615814</v>
       </c>
       <c r="E1495" t="n">
-        <v>1.85000002384186</v>
+        <v>1.80999994277954</v>
       </c>
       <c r="F1495" t="n">
-        <v>1.85000002384186</v>
+        <v>1.82500004768372</v>
       </c>
       <c r="G1495" t="s">
         <v>7</v>
@@ -34759,22 +34759,22 @@
     </row>
     <row r="1496">
       <c r="A1496" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1496" t="n">
-        <v>10800</v>
+        <v>35100</v>
       </c>
       <c r="C1496" t="n">
-        <v>1.79499995708466</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="D1496" t="n">
-        <v>1.76499998569489</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="E1496" t="n">
-        <v>1.7849999666214</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="F1496" t="n">
-        <v>1.78999996185303</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="G1496" t="s">
         <v>7</v>
@@ -34782,22 +34782,22 @@
     </row>
     <row r="1497">
       <c r="A1497" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1497" t="n">
-        <v>18900</v>
+        <v>10800</v>
       </c>
       <c r="C1497" t="n">
-        <v>1.75999999046326</v>
+        <v>1.79499995708466</v>
       </c>
       <c r="D1497" t="n">
-        <v>1.71000003814697</v>
+        <v>1.76499998569489</v>
       </c>
       <c r="E1497" t="n">
-        <v>1.75</v>
+        <v>1.7849999666214</v>
       </c>
       <c r="F1497" t="n">
-        <v>1.71000003814697</v>
+        <v>1.78999996185303</v>
       </c>
       <c r="G1497" t="s">
         <v>7</v>
@@ -34805,22 +34805,22 @@
     </row>
     <row r="1498">
       <c r="A1498" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1498" t="n">
         <v>18900</v>
       </c>
       <c r="C1498" t="n">
-        <v>1.73500001430511</v>
+        <v>1.75999999046326</v>
       </c>
       <c r="D1498" t="n">
-        <v>1.64999997615814</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="E1498" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F1498" t="n">
         <v>1.71000003814697</v>
-      </c>
-      <c r="F1498" t="n">
-        <v>1.66499996185303</v>
       </c>
       <c r="G1498" t="s">
         <v>7</v>
@@ -34828,24 +34828,47 @@
     </row>
     <row r="1499">
       <c r="A1499" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1499" t="n">
-        <v>11700</v>
+        <v>18900</v>
       </c>
       <c r="C1499" t="n">
-        <v>1.73000001907349</v>
+        <v>1.73500001430511</v>
       </c>
       <c r="D1499" t="n">
-        <v>1.69500005245209</v>
+        <v>1.64999997615814</v>
       </c>
       <c r="E1499" t="n">
-        <v>1.70000004768372</v>
+        <v>1.71000003814697</v>
       </c>
       <c r="F1499" t="n">
-        <v>1.73000001907349</v>
+        <v>1.66499996185303</v>
       </c>
       <c r="G1499" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1500" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C1500" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G1500" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -39427,6 +39427,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1503" t="n">
+        <v>23400</v>
+      </c>
+      <c r="C1503" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>1.65499997138977</v>
+      </c>
+      <c r="H1503" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -39453,6 +39453,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1504" t="n">
+        <v>20700</v>
+      </c>
+      <c r="C1504" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>1.67499995231628</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="H1504" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -39479,6 +39479,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1505" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C1505" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="H1505" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -39505,6 +39505,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1506" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="H1506" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -39583,6 +39583,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1509" t="n">
+        <v>17100</v>
+      </c>
+      <c r="C1509" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>1.76499998569489</v>
+      </c>
+      <c r="H1509" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -35141,8 +35141,31 @@
       <c r="E1512" t="n">
         <v>1.44000005722046</v>
       </c>
-      <c r="F1512"/>
+      <c r="F1512" t="n">
+        <v>1.45500004291534</v>
+      </c>
       <c r="G1512" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1513" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C1513" t="n">
+        <v>1.4650000333786</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F1513"/>
+      <c r="G1513" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -35164,8 +35164,31 @@
       <c r="E1513" t="n">
         <v>1.39999997615814</v>
       </c>
-      <c r="F1513"/>
+      <c r="F1513" t="n">
+        <v>1.4650000333786</v>
+      </c>
       <c r="G1513" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1514" t="n">
+        <v>51300</v>
+      </c>
+      <c r="C1514" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F1514"/>
+      <c r="G1514" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -35187,8 +35187,31 @@
       <c r="E1514" t="n">
         <v>1.39999997615814</v>
       </c>
-      <c r="F1514"/>
+      <c r="F1514" t="n">
+        <v>1.375</v>
+      </c>
       <c r="G1514" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1515" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1515" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F1515"/>
+      <c r="G1515" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -35210,8 +35210,31 @@
       <c r="E1515" t="n">
         <v>1.35000002384186</v>
       </c>
-      <c r="F1515"/>
+      <c r="F1515" t="n">
+        <v>1.37000000476837</v>
+      </c>
       <c r="G1515" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1516" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C1516" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="F1516"/>
+      <c r="G1516" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -35240,6 +35240,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1517">
+      <c r="A1517" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1517" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1517" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="G1517" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -39869,6 +39869,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1520">
+      <c r="A1520" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1520" t="n">
+        <v>9900</v>
+      </c>
+      <c r="C1520" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H1520" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -39895,6 +39895,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1521">
+      <c r="A1521" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1521" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C1521" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="D1521" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="H1521" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -44487,6 +44487,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1522">
+      <c r="A1522" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1522" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1522" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I1522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1523" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1523" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>900</v>
+      </c>
+      <c r="I1523" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -44545,6 +44545,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1524">
+      <c r="A1524" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1524" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>1.50499999523163</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I1524" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -44574,6 +44574,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1525">
+      <c r="A1525" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1525" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1525" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>1.54499995708466</v>
+      </c>
+      <c r="H1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1526" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1526" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>1.47500002384186</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>1.48000001907349</v>
+      </c>
+      <c r="H1526" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I1526" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -44632,6 +44632,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1527">
+      <c r="A1527" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1527" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1527" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="D1527" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>1.49000000953674</v>
+      </c>
+      <c r="H1527" t="n">
+        <v>900</v>
+      </c>
+      <c r="I1527" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -44661,6 +44661,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1528">
+      <c r="A1528" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1528" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1528" t="n">
+        <v>1.51499998569489</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>1.51499998569489</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>1.51499998569489</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>1.51499998569489</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>1.51499998569489</v>
+      </c>
+      <c r="H1528" t="n">
+        <v>900</v>
+      </c>
+      <c r="I1528" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -44690,6 +44690,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1529">
+      <c r="A1529" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1529" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1529" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="H1529" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I1529" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ESIGM.MI.xlsx
+++ b/data/ESIGM.MI.xlsx
@@ -44719,6 +44719,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1530">
+      <c r="A1530" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1530" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1530" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="G1530" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="H1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1531" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1531" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>1.52499997615814</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1531" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1531" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1531" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
